--- a/excel_data/CookieConsent.xlsx
+++ b/excel_data/CookieConsent.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E379"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,9 +433,4834 @@
         <v>73.8066049</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>user_7rp4otcbi</v>
+      </c>
+      <c r="B3" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C3" t="str">
+        <v>2025-07-30T05:17:41.517Z</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>user_ceaybsep8</v>
+      </c>
+      <c r="B4" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C4" t="str">
+        <v>2025-08-13T04:03:20.886Z</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>user_073j62kcp</v>
+      </c>
+      <c r="B5" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C5" t="str">
+        <v>2025-08-13T04:38:14.849Z</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>user_9jr3rwvn6</v>
+      </c>
+      <c r="B6" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C6" t="str">
+        <v>2025-08-13T05:26:55.221Z</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>user_hi68csxfg</v>
+      </c>
+      <c r="B7" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C7" t="str">
+        <v>2025-08-13T08:04:51.852Z</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>user_kwdhtwctb</v>
+      </c>
+      <c r="B8" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C8" t="str">
+        <v>2025-08-13T08:33:22.303Z</v>
+      </c>
+      <c r="D8">
+        <v>22.4657408</v>
+      </c>
+      <c r="E8">
+        <v>88.3032064</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>user_vqtj18yws</v>
+      </c>
+      <c r="B9" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C9" t="str">
+        <v>2025-08-13T08:50:56.338Z</v>
+      </c>
+      <c r="D9">
+        <v>18.624272</v>
+      </c>
+      <c r="E9">
+        <v>73.9139778</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>user_p1pajwax1</v>
+      </c>
+      <c r="B10" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C10" t="str">
+        <v>2025-08-13T09:14:11.421Z</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>user_iriz44qev</v>
+      </c>
+      <c r="B11" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C11" t="str">
+        <v>2025-08-13T11:17:05.359Z</v>
+      </c>
+      <c r="D11">
+        <v>17.6785248</v>
+      </c>
+      <c r="E11">
+        <v>73.9947448</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>user_8z117tawr</v>
+      </c>
+      <c r="B12" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C12" t="str">
+        <v>2025-08-13T13:08:35.672Z</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>user_2mrqfpnep</v>
+      </c>
+      <c r="B13" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C13" t="str">
+        <v>2025-08-14T00:00:07.856Z</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>user_gb4ws175p</v>
+      </c>
+      <c r="B14" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C14" t="str">
+        <v>2025-08-15T00:00:01.782Z</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>user_fibbng1pb</v>
+      </c>
+      <c r="B15" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C15" t="str">
+        <v>2025-08-16T05:53:49.947Z</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>user_8dhrnx0kl</v>
+      </c>
+      <c r="B16" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C16" t="str">
+        <v>2025-08-16T16:07:31.149Z</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>user_7zfh6kqxh</v>
+      </c>
+      <c r="B17" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C17" t="str">
+        <v>2025-08-17T05:08:37.325Z</v>
+      </c>
+      <c r="D17">
+        <v>18.4854756</v>
+      </c>
+      <c r="E17">
+        <v>73.8167605</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>user_cyzq2avav</v>
+      </c>
+      <c r="B18" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C18" t="str">
+        <v>2025-08-17T06:55:06.937Z</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>user_l917zmucd</v>
+      </c>
+      <c r="B19" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C19" t="str">
+        <v>2025-08-17T16:15:16.332Z</v>
+      </c>
+      <c r="D19">
+        <v>18.5925632</v>
+      </c>
+      <c r="E19">
+        <v>73.924608</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>user_n7vscbabj</v>
+      </c>
+      <c r="B20" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C20" t="str">
+        <v>2025-08-18T04:08:04.665Z</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>user_vrqy3ccrk</v>
+      </c>
+      <c r="B21" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C21" t="str">
+        <v>2025-08-18T04:49:11.429Z</v>
+      </c>
+      <c r="D21">
+        <v>18.4909824</v>
+      </c>
+      <c r="E21">
+        <v>73.8033664</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>user_ezn8ww4ni</v>
+      </c>
+      <c r="B22" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C22" t="str">
+        <v>2025-08-18T11:38:46.395Z</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>user_qm22fue59</v>
+      </c>
+      <c r="B23" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C23" t="str">
+        <v>2025-08-19T05:02:12.896Z</v>
+      </c>
+      <c r="D23">
+        <v>18.487199</v>
+      </c>
+      <c r="E23">
+        <v>73.7958835</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>user_9d74algua</v>
+      </c>
+      <c r="B24" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C24" t="str">
+        <v>2025-08-20T17:41:05.141Z</v>
+      </c>
+      <c r="D24">
+        <v>15.9186944</v>
+      </c>
+      <c r="E24">
+        <v>76.0119296</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>user_zmioddski</v>
+      </c>
+      <c r="B25" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C25" t="str">
+        <v>2025-08-22T06:57:43.235Z</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>user_mvcufyesw</v>
+      </c>
+      <c r="B26" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C26" t="str">
+        <v>2025-08-22T12:07:19.283Z</v>
+      </c>
+      <c r="D26">
+        <v>28.5383703</v>
+      </c>
+      <c r="E26">
+        <v>77.2119311</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>user_ym4xvyf19</v>
+      </c>
+      <c r="B27" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C27" t="str">
+        <v>2025-08-24T16:27:59.293Z</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>user_ddcfrf9bx</v>
+      </c>
+      <c r="B28" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C28" t="str">
+        <v>2025-08-25T14:32:56.681Z</v>
+      </c>
+      <c r="D28">
+        <v>18.4896422</v>
+      </c>
+      <c r="E28">
+        <v>73.8175388</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>user_moljahmt6</v>
+      </c>
+      <c r="B29" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C29" t="str">
+        <v>2025-08-26T09:47:49.754Z</v>
+      </c>
+      <c r="D29">
+        <v>18.48724019607843</v>
+      </c>
+      <c r="E29">
+        <v>73.79583911764706</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>user_3ib1h5m6i</v>
+      </c>
+      <c r="B30" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C30" t="str">
+        <v>2025-08-26T12:30:08.823Z</v>
+      </c>
+      <c r="D30">
+        <v>18.587336385231527</v>
+      </c>
+      <c r="E30">
+        <v>73.88713833971728</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>user_hyboh7u1h</v>
+      </c>
+      <c r="B31" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C31" t="str">
+        <v>2025-08-26T16:22:35.055Z</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>user_ik626k0ds</v>
+      </c>
+      <c r="B32" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C32" t="str">
+        <v>2025-08-28T09:30:51.196Z</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>user_bhro49k72</v>
+      </c>
+      <c r="B33" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C33" t="str">
+        <v>2025-08-28T09:58:10.036Z</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>user_8msidpiee</v>
+      </c>
+      <c r="B34" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C34" t="str">
+        <v>2025-08-28T20:15:55.650Z</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>user_tfquuzf3z</v>
+      </c>
+      <c r="B35" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C35" t="str">
+        <v>2025-08-30T13:36:38.532Z</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>user_6kvm412ju</v>
+      </c>
+      <c r="B36" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C36" t="str">
+        <v>2025-08-31T09:30:06.135Z</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>user_foigiqg4w</v>
+      </c>
+      <c r="B37" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C37" t="str">
+        <v>2025-09-01T10:30:00.244Z</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>user_jd05okev7</v>
+      </c>
+      <c r="B38" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C38" t="str">
+        <v>2025-09-03T08:57:02.257Z</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>user_ndd3is0l8</v>
+      </c>
+      <c r="B39" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C39" t="str">
+        <v>2025-09-05T06:21:13.974Z</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>user_nn1gk71jf</v>
+      </c>
+      <c r="B40" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C40" t="str">
+        <v>2025-09-05T08:08:52.465Z</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>user_703lv7kvp</v>
+      </c>
+      <c r="B41" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C41" t="str">
+        <v>2025-09-05T15:06:10.815Z</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>user_3fb2zrgi2</v>
+      </c>
+      <c r="B42" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C42" t="str">
+        <v>2025-09-06T03:30:24.367Z</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>user_kz1vq6efc</v>
+      </c>
+      <c r="B43" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C43" t="str">
+        <v>2025-09-07T17:14:39.835Z</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>user_3855cwtr2</v>
+      </c>
+      <c r="B44" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C44" t="str">
+        <v>2025-09-08T10:23:07.354Z</v>
+      </c>
+      <c r="D44">
+        <v>18.486432117638525</v>
+      </c>
+      <c r="E44">
+        <v>73.7961018910647</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>user_i3j3slwzj</v>
+      </c>
+      <c r="B45" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C45" t="str">
+        <v>2025-09-08T10:29:06.219Z</v>
+      </c>
+      <c r="D45">
+        <v>22.5709313</v>
+      </c>
+      <c r="E45">
+        <v>73.642536</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>user_t8222b8s2</v>
+      </c>
+      <c r="B46" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C46" t="str">
+        <v>2025-09-08T12:05:39.819Z</v>
+      </c>
+      <c r="D46">
+        <v>18.4418304</v>
+      </c>
+      <c r="E46">
+        <v>73.7837056</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>user_oq0kl1eib</v>
+      </c>
+      <c r="B47" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C47" t="str">
+        <v>2025-09-08T15:11:08.552Z</v>
+      </c>
+      <c r="D47">
+        <v>18.5575562</v>
+      </c>
+      <c r="E47">
+        <v>73.9090628</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>user_j9mk54cuf</v>
+      </c>
+      <c r="B48" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C48" t="str">
+        <v>2025-09-09T11:01:13.339Z</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>user_i35du01ec</v>
+      </c>
+      <c r="B49" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C49" t="str">
+        <v>2025-09-09T11:40:00.237Z</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>user_ooaofnwgp</v>
+      </c>
+      <c r="B50" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C50" t="str">
+        <v>2025-09-09T12:40:21.985Z</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>user_1vs9o538x</v>
+      </c>
+      <c r="B51" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C51" t="str">
+        <v>2025-09-09T13:57:29.657Z</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>user_28suvrhal</v>
+      </c>
+      <c r="B52" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C52" t="str">
+        <v>2025-09-10T05:57:56.915Z</v>
+      </c>
+      <c r="D52">
+        <v>18.4418304</v>
+      </c>
+      <c r="E52">
+        <v>73.7837056</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>user_28suvrhal</v>
+      </c>
+      <c r="B53" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C53" t="str">
+        <v>2025-09-10T05:58:25.738Z</v>
+      </c>
+      <c r="D53">
+        <v>18.4418304</v>
+      </c>
+      <c r="E53">
+        <v>73.7837056</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>user_04vlnw0h3</v>
+      </c>
+      <c r="B54" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C54" t="str">
+        <v>2025-09-12T09:31:40.439Z</v>
+      </c>
+      <c r="D54">
+        <v>18.6071432</v>
+      </c>
+      <c r="E54">
+        <v>73.8257211</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>user_j447r4j8j</v>
+      </c>
+      <c r="B55" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C55" t="str">
+        <v>2025-09-12T09:53:47.349Z</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>user_26ffzqd57</v>
+      </c>
+      <c r="B56" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C56" t="str">
+        <v>2025-09-12T11:15:49.112Z</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>user_8s4oj73i7</v>
+      </c>
+      <c r="B57" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C57" t="str">
+        <v>2025-09-15T17:01:39.916Z</v>
+      </c>
+      <c r="D57">
+        <v>17.3965312</v>
+      </c>
+      <c r="E57">
+        <v>78.5317888</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>user_dnexiuqkb</v>
+      </c>
+      <c r="B58" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C58" t="str">
+        <v>2025-09-16T14:58:45.606Z</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>user_z2oeru0uf</v>
+      </c>
+      <c r="B59" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C59" t="str">
+        <v>2025-09-17T08:55:24.942Z</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>user_4lpkvidyx</v>
+      </c>
+      <c r="B60" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C60" t="str">
+        <v>2025-09-17T09:49:16.054Z</v>
+      </c>
+      <c r="D60">
+        <v>22.5869824</v>
+      </c>
+      <c r="E60">
+        <v>88.4047872</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>user_uzxwmzg91</v>
+      </c>
+      <c r="B61" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C61" t="str">
+        <v>2025-09-17T11:06:17.294Z</v>
+      </c>
+      <c r="D61">
+        <v>18.486865489503796</v>
+      </c>
+      <c r="E61">
+        <v>73.79614906208684</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>user_r0w9jpnr3</v>
+      </c>
+      <c r="B62" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C62" t="str">
+        <v>2025-09-18T10:01:07.678Z</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>user_3qq4lwstn</v>
+      </c>
+      <c r="B63" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C63" t="str">
+        <v>2025-09-19T00:25:00.461Z</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>user_wozgfa082</v>
+      </c>
+      <c r="B64" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C64" t="str">
+        <v>2025-09-19T05:22:48.442Z</v>
+      </c>
+      <c r="D64">
+        <v>18.493547325715</v>
+      </c>
+      <c r="E64">
+        <v>73.78852999999998</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>user_wp90az9wc</v>
+      </c>
+      <c r="B65" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C65" t="str">
+        <v>2025-09-19T05:24:00.079Z</v>
+      </c>
+      <c r="D65">
+        <v>18.4612036</v>
+      </c>
+      <c r="E65">
+        <v>73.8452743</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>user_o1mowr5wv</v>
+      </c>
+      <c r="B66" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C66" t="str">
+        <v>2025-09-19T14:57:39.625Z</v>
+      </c>
+      <c r="D66">
+        <v>23.9337472</v>
+      </c>
+      <c r="E66">
+        <v>88.2540544</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>user_de61pg5pe</v>
+      </c>
+      <c r="B67" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C67" t="str">
+        <v>2025-09-20T04:51:23.286Z</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>user_9wtqn6f1r</v>
+      </c>
+      <c r="B68" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C68" t="str">
+        <v>2025-09-20T04:51:21.250Z</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>user_tfxfdci5v</v>
+      </c>
+      <c r="B69" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C69" t="str">
+        <v>2025-09-20T16:52:24.870Z</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>user_5ql4l4lt0</v>
+      </c>
+      <c r="B70" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C70" t="str">
+        <v>2025-09-21T07:34:48.023Z</v>
+      </c>
+      <c r="D70">
+        <v>28.4739961</v>
+      </c>
+      <c r="E70">
+        <v>77.3247241</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>user_pkwdab8vn</v>
+      </c>
+      <c r="B71" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C71" t="str">
+        <v>2025-09-21T14:41:12.078Z</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>user_qiuhuol16</v>
+      </c>
+      <c r="B72" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C72" t="str">
+        <v>2025-09-22T09:46:24.468Z</v>
+      </c>
+      <c r="D72">
+        <v>18.4874938</v>
+      </c>
+      <c r="E72">
+        <v>73.7964216</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>user_raylrs8ya</v>
+      </c>
+      <c r="B73" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C73" t="str">
+        <v>2025-09-22T10:38:09.025Z</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>user_yuimohadj</v>
+      </c>
+      <c r="B74" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C74" t="str">
+        <v>2025-09-23T21:15:37.667Z</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>user_ujuyd19uy</v>
+      </c>
+      <c r="B75" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C75" t="str">
+        <v>2025-09-25T10:47:25.443Z</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>user_s5nbbja2g</v>
+      </c>
+      <c r="B76" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C76" t="str">
+        <v>2025-09-28T10:17:10.989Z</v>
+      </c>
+      <c r="D76">
+        <v>18.441212522969327</v>
+      </c>
+      <c r="E76">
+        <v>73.84675948997342</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>user_5jvjl2c5e</v>
+      </c>
+      <c r="B77" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C77" t="str">
+        <v>2025-09-30T15:14:01.385Z</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>user_6h703ta5y</v>
+      </c>
+      <c r="B78" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C78" t="str">
+        <v>2025-10-01T04:31:36.308Z</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>user_g8qx31l8s</v>
+      </c>
+      <c r="B79" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C79" t="str">
+        <v>2025-10-01T16:33:24.799Z</v>
+      </c>
+      <c r="D79">
+        <v>47.379416799563295</v>
+      </c>
+      <c r="E79">
+        <v>8.531599622138334</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>user_lkzhf9tif</v>
+      </c>
+      <c r="B80" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C80" t="str">
+        <v>2025-10-02T04:34:52.713Z</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>user_xix0xd8tq</v>
+      </c>
+      <c r="B81" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C81" t="str">
+        <v>2025-10-03T10:56:23.968Z</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>user_6iqkka6kj</v>
+      </c>
+      <c r="B82" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C82" t="str">
+        <v>2025-10-03T19:19:51.808Z</v>
+      </c>
+      <c r="D82">
+        <v>26.707091657129634</v>
+      </c>
+      <c r="E82">
+        <v>88.34806276141988</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>user_g9grqlcd9</v>
+      </c>
+      <c r="B83" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C83" t="str">
+        <v>2025-10-07T06:24:12.604Z</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>user_tc2njggyh</v>
+      </c>
+      <c r="B84" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C84" t="str">
+        <v>2025-10-07T10:34:32.699Z</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>user_l6gnot03n</v>
+      </c>
+      <c r="B85" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C85" t="str">
+        <v>2025-10-07T16:20:40.519Z</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>user_ljgc9b7b0</v>
+      </c>
+      <c r="B86" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C86" t="str">
+        <v>2025-10-09T07:09:01.013Z</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>user_swvzsd1uf</v>
+      </c>
+      <c r="B87" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C87" t="str">
+        <v>2025-10-09T21:26:49.540Z</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>user_grdmowpvm</v>
+      </c>
+      <c r="B88" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C88" t="str">
+        <v>2025-10-10T05:15:10.955Z</v>
+      </c>
+      <c r="D88">
+        <v>20.8969031</v>
+      </c>
+      <c r="E88">
+        <v>77.7528972</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>user_i5duh8k38</v>
+      </c>
+      <c r="B89" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C89" t="str">
+        <v>2025-10-07T08:46:32.200Z</v>
+      </c>
+      <c r="D89">
+        <v>23.2164638</v>
+      </c>
+      <c r="E89">
+        <v>77.389849</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>user_cfjix0xps</v>
+      </c>
+      <c r="B90" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C90" t="str">
+        <v>2025-10-11T06:37:20.648Z</v>
+      </c>
+      <c r="D90">
+        <v>23.2111256</v>
+      </c>
+      <c r="E90">
+        <v>77.3934829</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>user_d39wsxwq2</v>
+      </c>
+      <c r="B91" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C91" t="str">
+        <v>2025-10-11T18:02:58.955Z</v>
+      </c>
+      <c r="D91">
+        <v>13.069127912945293</v>
+      </c>
+      <c r="E91">
+        <v>77.58947580356687</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>user_snkmngi71</v>
+      </c>
+      <c r="B92" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C92" t="str">
+        <v>2025-10-12T20:22:29.677Z</v>
+      </c>
+      <c r="D92">
+        <v>20.35637386815092</v>
+      </c>
+      <c r="E92">
+        <v>85.81930465465372</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>user_967rlq96i</v>
+      </c>
+      <c r="B93" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C93" t="str">
+        <v>2025-10-13T06:31:27.417Z</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>user_efaj8zseo</v>
+      </c>
+      <c r="B94" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C94" t="str">
+        <v>2025-10-13T06:32:48.108Z</v>
+      </c>
+      <c r="D94">
+        <v>12.939988039673322</v>
+      </c>
+      <c r="E94">
+        <v>77.58504393184303</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>user_801013le4</v>
+      </c>
+      <c r="B95" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C95" t="str">
+        <v>2025-10-13T11:05:47.082Z</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>user_56hbe1tq1</v>
+      </c>
+      <c r="B96" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C96" t="str">
+        <v>2025-10-14T12:48:45.138Z</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>user_0sce2rfkc</v>
+      </c>
+      <c r="B97" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C97" t="str">
+        <v>2025-10-15T04:36:17.518Z</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>user_a18wk7aor</v>
+      </c>
+      <c r="B98" t="str">
+        <v>59.185.107.5</v>
+      </c>
+      <c r="C98" t="str">
+        <v>2025-10-15T05:20:22.197Z</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>user_zl44je1mx</v>
+      </c>
+      <c r="B99" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C99" t="str">
+        <v>2025-10-15T08:38:50.074Z</v>
+      </c>
+      <c r="D99">
+        <v>18.548722811642342</v>
+      </c>
+      <c r="E99">
+        <v>73.82693887143495</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>user_6m9numcv8</v>
+      </c>
+      <c r="B100" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C100" t="str">
+        <v>2025-10-16T00:32:13.081Z</v>
+      </c>
+      <c r="D100">
+        <v>18.486168</v>
+      </c>
+      <c r="E100">
+        <v>73.796841</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>user_2jn9toc6p</v>
+      </c>
+      <c r="B101" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C101" t="str">
+        <v>2025-10-18T01:53:16.099Z</v>
+      </c>
+      <c r="D101">
+        <v>28.61</v>
+      </c>
+      <c r="E101">
+        <v>77.23</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>user_nkpj5bzoa</v>
+      </c>
+      <c r="B102" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C102" t="str">
+        <v>2025-10-19T19:59:25.531Z</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>user_lhbl30axb</v>
+      </c>
+      <c r="B103" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C103" t="str">
+        <v>2025-10-22T02:22:34.364Z</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>user_bzi3el8lr</v>
+      </c>
+      <c r="B104" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C104" t="str">
+        <v>2025-10-24T04:32:30.675Z</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>user_utf0ffgs5</v>
+      </c>
+      <c r="B105" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C105" t="str">
+        <v>2025-10-24T08:30:11.019Z</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>user_4u10t5uue</v>
+      </c>
+      <c r="B106" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C106" t="str">
+        <v>2025-10-24T12:23:43.843Z</v>
+      </c>
+      <c r="D106">
+        <v>17.6542118</v>
+      </c>
+      <c r="E106">
+        <v>78.8252171</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>user_uztg0izsi</v>
+      </c>
+      <c r="B107" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C107" t="str">
+        <v>2025-10-25T06:27:00.075Z</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>user_f17iou3d3</v>
+      </c>
+      <c r="B108" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C108" t="str">
+        <v>2025-10-26T08:28:05.048Z</v>
+      </c>
+      <c r="D108">
+        <v>20.9289315</v>
+      </c>
+      <c r="E108">
+        <v>77.7498043</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>user_1lth0lbim</v>
+      </c>
+      <c r="B109" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C109" t="str">
+        <v>2025-10-29T06:45:26.586Z</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>user_8w522yokt</v>
+      </c>
+      <c r="B110" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C110" t="str">
+        <v>2025-10-29T10:17:17.231Z</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>user_pi6k1d0rs</v>
+      </c>
+      <c r="B111" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C111" t="str">
+        <v>2025-10-29T11:11:50.148Z</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>user_izflnqys6</v>
+      </c>
+      <c r="B112" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C112" t="str">
+        <v>2025-10-30T09:11:34.494Z</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>user_70ncp11zm</v>
+      </c>
+      <c r="B113" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C113" t="str">
+        <v>2025-10-30T13:37:51.749Z</v>
+      </c>
+      <c r="D113">
+        <v>19.5283385</v>
+      </c>
+      <c r="E113">
+        <v>74.07689</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>user_n06o8u53h</v>
+      </c>
+      <c r="B114" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C114" t="str">
+        <v>2025-10-31T07:08:27.974Z</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>user_0zqqjdf4k</v>
+      </c>
+      <c r="B115" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C115" t="str">
+        <v>2025-10-31T07:54:20.044Z</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>user_hfw1c9ltc</v>
+      </c>
+      <c r="B116" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C116" t="str">
+        <v>2025-10-31T08:00:48.428Z</v>
+      </c>
+      <c r="D116">
+        <v>18.4973318</v>
+      </c>
+      <c r="E116">
+        <v>73.8117517</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>user_7nsrxhfy7</v>
+      </c>
+      <c r="B117" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C117" t="str">
+        <v>2025-10-31T08:05:56.604Z</v>
+      </c>
+      <c r="D117">
+        <v>20.340608</v>
+      </c>
+      <c r="E117">
+        <v>85.8178939</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>user_s8pnkyg4o</v>
+      </c>
+      <c r="B118" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C118" t="str">
+        <v>2025-11-01T13:58:50.114Z</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>user_xap7wchy2</v>
+      </c>
+      <c r="B119" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C119" t="str">
+        <v>2025-11-02T14:28:30.324Z</v>
+      </c>
+      <c r="D119">
+        <v>18.4830178</v>
+      </c>
+      <c r="E119">
+        <v>73.8105224</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>user_a74bc6b1l</v>
+      </c>
+      <c r="B120" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C120" t="str">
+        <v>2025-11-03T08:35:28.843Z</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>user_0mzbejpqd</v>
+      </c>
+      <c r="B121" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C121" t="str">
+        <v>2025-11-03T10:23:21.209Z</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>user_wnj17g8n1</v>
+      </c>
+      <c r="B122" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C122" t="str">
+        <v>2025-11-03T13:46:56.782Z</v>
+      </c>
+      <c r="D122">
+        <v>18.4891952</v>
+      </c>
+      <c r="E122">
+        <v>73.810474</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>user_9bifuadjc</v>
+      </c>
+      <c r="B123" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C123" t="str">
+        <v>2025-11-04T05:57:04.861Z</v>
+      </c>
+      <c r="D123">
+        <v>28.6848308</v>
+      </c>
+      <c r="E123">
+        <v>77.3274536</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>user_hqub504op</v>
+      </c>
+      <c r="B124" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C124" t="str">
+        <v>2025-11-05T13:27:38.464Z</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>user_bpzk01c88</v>
+      </c>
+      <c r="B125" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C125" t="str">
+        <v>2025-11-06T07:27:07.731Z</v>
+      </c>
+      <c r="D125">
+        <v>18.483175</v>
+      </c>
+      <c r="E125">
+        <v>73.8105354</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>user_t5i04qzfy</v>
+      </c>
+      <c r="B126" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C126" t="str">
+        <v>2025-11-06T12:30:43.742Z</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>user_u23l2tkjo</v>
+      </c>
+      <c r="B127" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C127" t="str">
+        <v>2025-11-07T03:52:45.062Z</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>user_ybpo76bzu</v>
+      </c>
+      <c r="B128" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C128" t="str">
+        <v>2025-11-07T13:20:00.643Z</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>user_iau38wspw</v>
+      </c>
+      <c r="B129" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C129" t="str">
+        <v>2025-11-08T01:17:06.899Z</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>user_6agonbg2v</v>
+      </c>
+      <c r="B130" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C130" t="str">
+        <v>2025-11-08T05:07:52.753Z</v>
+      </c>
+      <c r="D130">
+        <v>20.2959847</v>
+      </c>
+      <c r="E130">
+        <v>85.8246101</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>user_rd1dvco70</v>
+      </c>
+      <c r="B131" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C131" t="str">
+        <v>2025-11-08T05:17:39.351Z</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>user_uceqk9inu</v>
+      </c>
+      <c r="B132" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C132" t="str">
+        <v>2025-11-08T06:45:19.558Z</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>user_5l1jaarht</v>
+      </c>
+      <c r="B133" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C133" t="str">
+        <v>2025-11-08T06:52:42.357Z</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>user_24kcf1n1x</v>
+      </c>
+      <c r="B134" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C134" t="str">
+        <v>2025-11-08T06:56:21.320Z</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>user_0cuipv5bd</v>
+      </c>
+      <c r="B135" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C135" t="str">
+        <v>2025-11-08T07:07:51.608Z</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>user_ghf3hejqn</v>
+      </c>
+      <c r="B136" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C136" t="str">
+        <v>2025-11-08T07:41:29.277Z</v>
+      </c>
+      <c r="D136">
+        <v>18.4947513</v>
+      </c>
+      <c r="E136">
+        <v>73.8543919</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>user_ok05uiori</v>
+      </c>
+      <c r="B137" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C137" t="str">
+        <v>2025-11-08T07:54:13.303Z</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>user_4mcek3gmu</v>
+      </c>
+      <c r="B138" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C138" t="str">
+        <v>2025-11-08T08:07:25.947Z</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>user_6dllk5jkl</v>
+      </c>
+      <c r="B139" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C139" t="str">
+        <v>2025-11-08T08:50:01.314Z</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>user_1lj7cfg7x</v>
+      </c>
+      <c r="B140" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C140" t="str">
+        <v>2025-11-08T09:29:21.579Z</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>user_67osch7tc</v>
+      </c>
+      <c r="B141" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C141" t="str">
+        <v>2025-11-08T09:31:18.574Z</v>
+      </c>
+      <c r="D141">
+        <v>51.54007253571595</v>
+      </c>
+      <c r="E141">
+        <v>0.08044063280194089</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>user_7pfgx15z1</v>
+      </c>
+      <c r="B142" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C142" t="str">
+        <v>2025-11-08T10:19:58.903Z</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>user_um2qnu7r4</v>
+      </c>
+      <c r="B143" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C143" t="str">
+        <v>2025-11-08T10:22:28.567Z</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>user_sirn5byhl</v>
+      </c>
+      <c r="B144" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C144" t="str">
+        <v>2025-11-08T10:33:33.684Z</v>
+      </c>
+      <c r="D144">
+        <v>17.0733029</v>
+      </c>
+      <c r="E144">
+        <v>81.8219549</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>user_a7gy68cd9</v>
+      </c>
+      <c r="B145" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C145" t="str">
+        <v>2025-11-08T10:39:57.351Z</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>user_fvhxvinm0</v>
+      </c>
+      <c r="B146" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C146" t="str">
+        <v>2025-11-08T10:42:47.917Z</v>
+      </c>
+      <c r="D146">
+        <v>18.5620347</v>
+      </c>
+      <c r="E146">
+        <v>73.9489743</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>user_sprtuta7c</v>
+      </c>
+      <c r="B147" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C147" t="str">
+        <v>2025-11-08T12:10:04.921Z</v>
+      </c>
+      <c r="D147">
+        <v>18.4874724</v>
+      </c>
+      <c r="E147">
+        <v>73.796467</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>user_2lx5kis3u</v>
+      </c>
+      <c r="B148" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C148" t="str">
+        <v>2025-11-08T12:22:58.903Z</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>user_lg93nzvqq</v>
+      </c>
+      <c r="B149" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C149" t="str">
+        <v>2025-11-08T15:04:48.746Z</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>user_nd7hxeiqm</v>
+      </c>
+      <c r="B150" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C150" t="str">
+        <v>2025-11-08T17:57:08.023Z</v>
+      </c>
+      <c r="D150">
+        <v>22.7081955</v>
+      </c>
+      <c r="E150">
+        <v>75.8824422</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>user_d21efh1jh</v>
+      </c>
+      <c r="B151" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C151" t="str">
+        <v>2025-11-09T06:10:01.630Z</v>
+      </c>
+      <c r="D151">
+        <v>9.755887526073618</v>
+      </c>
+      <c r="E151">
+        <v>76.64786004601224</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>user_62wuvuzs4</v>
+      </c>
+      <c r="B152" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C152" t="str">
+        <v>2025-11-09T13:53:32.151Z</v>
+      </c>
+      <c r="D152">
+        <v>17.4377154</v>
+      </c>
+      <c r="E152">
+        <v>78.4446316</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>user_a2j0mitxo</v>
+      </c>
+      <c r="B153" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C153" t="str">
+        <v>2025-11-10T06:43:48.255Z</v>
+      </c>
+      <c r="D153">
+        <v>21.13536</v>
+      </c>
+      <c r="E153">
+        <v>79.0822912</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>user_y3ura0t3x</v>
+      </c>
+      <c r="B154" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C154" t="str">
+        <v>2025-11-10T15:06:32.618Z</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>user_vb5b55gzw</v>
+      </c>
+      <c r="B155" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C155" t="str">
+        <v>2025-11-11T04:58:45.194Z</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>user_70o7389qs</v>
+      </c>
+      <c r="B156" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C156" t="str">
+        <v>2025-11-12T04:33:07.310Z</v>
+      </c>
+      <c r="D156">
+        <v>18.4834298</v>
+      </c>
+      <c r="E156">
+        <v>73.8021821</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>user_as0cf94oo</v>
+      </c>
+      <c r="B157" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C157" t="str">
+        <v>2025-11-12T05:24:15.336Z</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>user_3vn51njnf</v>
+      </c>
+      <c r="B158" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C158" t="str">
+        <v>2025-11-12T08:33:43.343Z</v>
+      </c>
+      <c r="D158">
+        <v>17.536017</v>
+      </c>
+      <c r="E158">
+        <v>78.2565423</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>user_qkw0t8i0u</v>
+      </c>
+      <c r="B159" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C159" t="str">
+        <v>2025-11-12T18:41:58.908Z</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>user_9ss96ai2o</v>
+      </c>
+      <c r="B160" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C160" t="str">
+        <v>2025-11-13T06:18:41.177Z</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>user_f1p6qoie6</v>
+      </c>
+      <c r="B161" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C161" t="str">
+        <v>2025-11-13T11:58:21.694Z</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>user_me80ugomf</v>
+      </c>
+      <c r="B162" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C162" t="str">
+        <v>2025-11-14T11:37:04.448Z</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>user_srkxf31yo</v>
+      </c>
+      <c r="B163" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C163" t="str">
+        <v>2025-11-14T19:01:20.890Z</v>
+      </c>
+      <c r="D163">
+        <v>18.5502596</v>
+      </c>
+      <c r="E163">
+        <v>73.8288008</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>user_ypa0x23ek</v>
+      </c>
+      <c r="B164" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C164" t="str">
+        <v>2025-11-15T12:10:09.040Z</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>user_8x0w53ncm</v>
+      </c>
+      <c r="B165" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C165" t="str">
+        <v>2025-11-16T16:21:52.816Z</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>user_54ct6iygf</v>
+      </c>
+      <c r="B166" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C166" t="str">
+        <v>2025-11-17T06:46:39.590Z</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>user_9s1hgcgs6</v>
+      </c>
+      <c r="B167" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C167" t="str">
+        <v>2025-11-17T17:11:23.166Z</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>user_o1o28fssc</v>
+      </c>
+      <c r="B168" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C168" t="str">
+        <v>2025-11-18T03:52:38.758Z</v>
+      </c>
+      <c r="D168">
+        <v>18.5957571</v>
+      </c>
+      <c r="E168">
+        <v>73.7998445</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>user_85tssgsr9</v>
+      </c>
+      <c r="B169" t="str">
+        <v>14.141.63.170</v>
+      </c>
+      <c r="C169" t="str">
+        <v>2025-11-18T06:41:57.045Z</v>
+      </c>
+      <c r="D169">
+        <v>18.8812665</v>
+      </c>
+      <c r="E169">
+        <v>72.938576</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>user_txsg487e4</v>
+      </c>
+      <c r="B170" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C170" t="str">
+        <v>2025-11-19T04:12:59.476Z</v>
+      </c>
+      <c r="D170">
+        <v>17.681858</v>
+      </c>
+      <c r="E170">
+        <v>74.0100441</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>user_fr9lvw5me</v>
+      </c>
+      <c r="B171" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C171" t="str">
+        <v>2025-11-19T09:32:56.003Z</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>user_c070uahm0</v>
+      </c>
+      <c r="B172" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C172" t="str">
+        <v>2025-11-19T11:17:44.219Z</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>user_j4fdqs18p</v>
+      </c>
+      <c r="B173" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C173" t="str">
+        <v>2025-11-19T14:16:40.530Z</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>user_a2yitonx3</v>
+      </c>
+      <c r="B174" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C174" t="str">
+        <v>2025-11-20T07:33:12.055Z</v>
+      </c>
+      <c r="D174">
+        <v>12.8492409</v>
+      </c>
+      <c r="E174">
+        <v>77.6671185</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>user_hnkqregwz</v>
+      </c>
+      <c r="B175" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C175" t="str">
+        <v>2025-11-20T07:50:27.260Z</v>
+      </c>
+      <c r="D175">
+        <v>18.4770708</v>
+      </c>
+      <c r="E175">
+        <v>73.7960289</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>user_uvjtgpz2i</v>
+      </c>
+      <c r="B176" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C176" t="str">
+        <v>2025-11-21T15:51:46.471Z</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>user_r5mihipmb</v>
+      </c>
+      <c r="B177" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C177" t="str">
+        <v>2025-11-22T10:37:36.236Z</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>user_y39uxfxf0</v>
+      </c>
+      <c r="B178" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C178" t="str">
+        <v>2025-11-22T12:39:16.277Z</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>user_qiw9y7p5t</v>
+      </c>
+      <c r="B179" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C179" t="str">
+        <v>2025-11-23T06:53:59.702Z</v>
+      </c>
+      <c r="D179">
+        <v>22.7421985</v>
+      </c>
+      <c r="E179">
+        <v>75.887761</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>user_m385kffmc</v>
+      </c>
+      <c r="B180" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C180" t="str">
+        <v>2025-11-23T07:02:11.945Z</v>
+      </c>
+      <c r="D180">
+        <v>18.4506709</v>
+      </c>
+      <c r="E180">
+        <v>73.8237537</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>user_posbn2y5w</v>
+      </c>
+      <c r="B181" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C181" t="str">
+        <v>2025-11-23T14:44:33.644Z</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>user_f6zd2l9ug</v>
+      </c>
+      <c r="B182" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C182" t="str">
+        <v>2025-11-24T06:28:03.206Z</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>user_o3hgmakx8</v>
+      </c>
+      <c r="B183" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C183" t="str">
+        <v>2025-11-25T02:03:38.878Z</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>user_27ru81bbq</v>
+      </c>
+      <c r="B184" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C184" t="str">
+        <v>2025-11-25T16:56:28.034Z</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>user_wrkkddpre</v>
+      </c>
+      <c r="B185" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C185" t="str">
+        <v>2025-11-25T16:56:32.099Z</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>user_v5oggohor</v>
+      </c>
+      <c r="B186" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C186" t="str">
+        <v>2025-11-26T07:44:25.675Z</v>
+      </c>
+      <c r="D186">
+        <v>19.246034309182352</v>
+      </c>
+      <c r="E186">
+        <v>73.12396956388484</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>user_mm4p2i4u5</v>
+      </c>
+      <c r="B187" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C187" t="str">
+        <v>2025-11-26T08:34:29.184Z</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>user_0orfgzehg</v>
+      </c>
+      <c r="B188" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C188" t="str">
+        <v>2025-11-26T10:27:39.003Z</v>
+      </c>
+      <c r="D188">
+        <v>17.6818532</v>
+      </c>
+      <c r="E188">
+        <v>74.0100457</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>user_94evnwki4</v>
+      </c>
+      <c r="B189" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C189" t="str">
+        <v>2025-11-26T17:14:16.496Z</v>
+      </c>
+      <c r="D189">
+        <v>18.6234297</v>
+      </c>
+      <c r="E189">
+        <v>73.7844909</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>user_p7zesrita</v>
+      </c>
+      <c r="B190" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C190" t="str">
+        <v>2025-11-29T10:40:18.415Z</v>
+      </c>
+      <c r="D190">
+        <v>20.153356</v>
+      </c>
+      <c r="E190">
+        <v>78.3093503</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>user_q28fvxyz4</v>
+      </c>
+      <c r="B191" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C191" t="str">
+        <v>2025-11-29T16:49:58.929Z</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>user_sgefgdey8</v>
+      </c>
+      <c r="B192" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C192" t="str">
+        <v>2025-12-01T10:55:16.911Z</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>user_xtfhqh1wd</v>
+      </c>
+      <c r="B193" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C193" t="str">
+        <v>2025-12-02T04:12:39.022Z</v>
+      </c>
+      <c r="D193">
+        <v>28.9744411</v>
+      </c>
+      <c r="E193">
+        <v>77.6389761</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>user_1lv9r6ixf</v>
+      </c>
+      <c r="B194" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C194" t="str">
+        <v>2025-12-04T17:14:46.617Z</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>user_z3ipfyh3b</v>
+      </c>
+      <c r="B195" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C195" t="str">
+        <v>2025-12-06T08:07:11.661Z</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>user_k57czswbj</v>
+      </c>
+      <c r="B196" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C196" t="str">
+        <v>2025-12-06T13:12:05.215Z</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>user_irwvqj9u8</v>
+      </c>
+      <c r="B197" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C197" t="str">
+        <v>2025-12-06T15:21:31.579Z</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>user_wnydq7ky2</v>
+      </c>
+      <c r="B198" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C198" t="str">
+        <v>2025-12-08T04:33:57.233Z</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>user_6a8nhgfta</v>
+      </c>
+      <c r="B199" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C199" t="str">
+        <v>2025-12-10T01:32:02.976Z</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>user_23lvhxygz</v>
+      </c>
+      <c r="B200" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C200" t="str">
+        <v>2025-12-10T12:30:09.599Z</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>user_btboa52fr</v>
+      </c>
+      <c r="B201" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C201" t="str">
+        <v>2025-12-10T16:52:15.314Z</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>user_12qeyi5pf</v>
+      </c>
+      <c r="B202" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C202" t="str">
+        <v>2025-12-11T10:47:16.861Z</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>user_8ilu0mot1</v>
+      </c>
+      <c r="B203" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C203" t="str">
+        <v>2025-12-11T13:04:19.926Z</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>user_ielhsbgnv</v>
+      </c>
+      <c r="B204" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C204" t="str">
+        <v>2025-12-15T14:02:31.679Z</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>user_sr2al4c49</v>
+      </c>
+      <c r="B205" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C205" t="str">
+        <v>2025-12-15T17:58:53.951Z</v>
+      </c>
+      <c r="D205">
+        <v>18.4888785</v>
+      </c>
+      <c r="E205">
+        <v>73.8108463</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>user_r5lnorhlg</v>
+      </c>
+      <c r="B206" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C206" t="str">
+        <v>2025-12-17T12:48:37.738Z</v>
+      </c>
+      <c r="D206">
+        <v>22.5762917</v>
+      </c>
+      <c r="E206">
+        <v>88.4119001</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>user_l14oc1j7g</v>
+      </c>
+      <c r="B207" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C207" t="str">
+        <v>2025-12-17T17:55:19.674Z</v>
+      </c>
+      <c r="D207">
+        <v>40.6943</v>
+      </c>
+      <c r="E207">
+        <v>-73.9249</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>user_yo3nqemjx</v>
+      </c>
+      <c r="B208" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C208" t="str">
+        <v>2025-12-20T21:44:15.744Z</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>user_8gj1izf1m</v>
+      </c>
+      <c r="B209" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C209" t="str">
+        <v>2025-12-21T09:54:45.957Z</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>user_rx0b46y3g</v>
+      </c>
+      <c r="B210" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C210" t="str">
+        <v>2025-12-21T13:36:48.572Z</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>user_zzqjbnrez</v>
+      </c>
+      <c r="B211" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C211" t="str">
+        <v>2025-12-23T20:21:02.679Z</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>user_8h0ryn7w6</v>
+      </c>
+      <c r="B212" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C212" t="str">
+        <v>2025-12-23T22:00:26.288Z</v>
+      </c>
+      <c r="D212">
+        <v>28.61</v>
+      </c>
+      <c r="E212">
+        <v>77.23</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>user_jlqao8syw</v>
+      </c>
+      <c r="B213" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C213" t="str">
+        <v>2025-12-24T06:36:01.087Z</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>user_bt4mayxj7</v>
+      </c>
+      <c r="B214" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C214" t="str">
+        <v>2025-12-27T05:11:44.305Z</v>
+      </c>
+      <c r="D214">
+        <v>28.6233715</v>
+      </c>
+      <c r="E214">
+        <v>77.3668853</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>user_zl2hfow2i</v>
+      </c>
+      <c r="B215" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C215" t="str">
+        <v>2025-12-27T16:51:15.146Z</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>user_452zfh8vc</v>
+      </c>
+      <c r="B216" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C216" t="str">
+        <v>2025-12-28T04:24:02.153Z</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>user_u09ey7fln</v>
+      </c>
+      <c r="B217" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C217" t="str">
+        <v>2025-12-29T06:55:32.083Z</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>user_09ggj7e72</v>
+      </c>
+      <c r="B218" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C218" t="str">
+        <v>2025-12-30T05:38:43.432Z</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>user_iixu40ltd</v>
+      </c>
+      <c r="B219" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C219" t="str">
+        <v>2026-01-01T04:42:54.981Z</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>user_sdw4xrqiz</v>
+      </c>
+      <c r="B220" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C220" t="str">
+        <v>2026-01-02T09:58:13.113Z</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>user_3rxukiufj</v>
+      </c>
+      <c r="B221" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C221" t="str">
+        <v>2026-01-02T12:55:41.083Z</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>user_j1nscjlbc</v>
+      </c>
+      <c r="B222" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C222" t="str">
+        <v>2026-01-02T17:47:53.484Z</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>user_fu040dubo</v>
+      </c>
+      <c r="B223" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C223" t="str">
+        <v>2026-01-03T06:50:12.057Z</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>user_bwj69norb</v>
+      </c>
+      <c r="B224" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C224" t="str">
+        <v>2026-01-03T09:16:21.676Z</v>
+      </c>
+      <c r="D224">
+        <v>18.50243133102697</v>
+      </c>
+      <c r="E224">
+        <v>73.81753340201955</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>user_e13sjy8aq</v>
+      </c>
+      <c r="B225" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C225" t="str">
+        <v>2026-01-04T04:28:43.033Z</v>
+      </c>
+      <c r="D225">
+        <v>18.4573971</v>
+      </c>
+      <c r="E225">
+        <v>73.7834326</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>user_jqyzofuvr</v>
+      </c>
+      <c r="B226" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C226" t="str">
+        <v>2026-01-04T12:21:40.786Z</v>
+      </c>
+      <c r="D226">
+        <v>22.5735231</v>
+      </c>
+      <c r="E226">
+        <v>88.4323462</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>user_gjj6trhrl</v>
+      </c>
+      <c r="B227" t="str">
+        <v>175.100.161.103</v>
+      </c>
+      <c r="C227" t="str">
+        <v>2026-01-05T08:35:40.503Z</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>user_bxhzperui</v>
+      </c>
+      <c r="B228" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C228" t="str">
+        <v>2026-01-08T06:33:03.808Z</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>user_uxoadlfwb</v>
+      </c>
+      <c r="B229" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C229" t="str">
+        <v>2026-01-08T14:05:21.944Z</v>
+      </c>
+      <c r="D229">
+        <v>17.3300173</v>
+      </c>
+      <c r="E229">
+        <v>76.8321968</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>user_4h7ljqk1o</v>
+      </c>
+      <c r="B230" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C230" t="str">
+        <v>2026-01-08T19:55:22.181Z</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>user_oujfxgvbb</v>
+      </c>
+      <c r="B231" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C231" t="str">
+        <v>2026-01-09T06:24:54.755Z</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>user_w438ix6yu</v>
+      </c>
+      <c r="B232" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C232" t="str">
+        <v>2026-01-10T01:33:25.929Z</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>user_477z7ognl</v>
+      </c>
+      <c r="B233" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C233" t="str">
+        <v>2026-01-10T11:01:13.627Z</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>user_0t1ujm4ap</v>
+      </c>
+      <c r="B234" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C234" t="str">
+        <v>2026-01-11T13:29:01.538Z</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>user_sauao6swl</v>
+      </c>
+      <c r="B235" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C235" t="str">
+        <v>2026-01-12T16:29:46.270Z</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>user_1j927bvk9</v>
+      </c>
+      <c r="B236" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C236" t="str">
+        <v>2026-01-15T05:51:58.277Z</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>user_um1zk0m8h</v>
+      </c>
+      <c r="B237" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C237" t="str">
+        <v>2026-01-15T09:39:58.265Z</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>user_zhb5eqrhc</v>
+      </c>
+      <c r="B238" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C238" t="str">
+        <v>2026-01-16T04:49:26.615Z</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>user_9udobco8g</v>
+      </c>
+      <c r="B239" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C239" t="str">
+        <v>2026-01-17T11:21:41.274Z</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>user_5iiqp40wn</v>
+      </c>
+      <c r="B240" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C240" t="str">
+        <v>2026-01-17T12:42:52.517Z</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>user_yxo1inx92</v>
+      </c>
+      <c r="B241" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C241" t="str">
+        <v>2026-01-18T17:52:22.343Z</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>user_ahwyopnil</v>
+      </c>
+      <c r="B242" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C242" t="str">
+        <v>2026-01-20T14:51:34.623Z</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>user_jwqiiayxq</v>
+      </c>
+      <c r="B243" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C243" t="str">
+        <v>2026-01-21T08:23:30.790Z</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>user_6qwmrd8j4</v>
+      </c>
+      <c r="B244" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C244" t="str">
+        <v>2026-01-22T06:53:59.246Z</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>user_uyk567ina</v>
+      </c>
+      <c r="B245" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C245" t="str">
+        <v>2026-01-22T18:21:03.482Z</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>user_up8i425vj</v>
+      </c>
+      <c r="B246" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C246" t="str">
+        <v>2026-01-26T12:17:34.656Z</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>user_xofnugq8h</v>
+      </c>
+      <c r="B247" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C247" t="str">
+        <v>2026-01-27T13:51:52.822Z</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>user_qfmynt5ok</v>
+      </c>
+      <c r="B248" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C248" t="str">
+        <v>2026-01-27T14:17:24.961Z</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>user_hy7924zzy</v>
+      </c>
+      <c r="B249" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C249" t="str">
+        <v>2026-01-28T06:18:42.816Z</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>user_ca88l0ba0</v>
+      </c>
+      <c r="B250" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C250" t="str">
+        <v>2026-01-28T11:32:37.548Z</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>user_8314dn98h</v>
+      </c>
+      <c r="B251" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C251" t="str">
+        <v>2026-01-28T12:59:37.898Z</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>user_fogcg46o9</v>
+      </c>
+      <c r="B252" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C252" t="str">
+        <v>2026-01-29T11:28:33.704Z</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>user_h4jasbfre</v>
+      </c>
+      <c r="B253" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C253" t="str">
+        <v>2026-02-01T06:17:45.866Z</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>user_sss5mv69k</v>
+      </c>
+      <c r="B254" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C254" t="str">
+        <v>2026-02-01T06:20:02.045Z</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>user_emh1aewgn</v>
+      </c>
+      <c r="B255" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C255" t="str">
+        <v>2026-02-02T05:12:34.948Z</v>
+      </c>
+      <c r="D255">
+        <v>18.4847927</v>
+      </c>
+      <c r="E255">
+        <v>73.7951961</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>user_m5wnhne6u</v>
+      </c>
+      <c r="B256" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C256" t="str">
+        <v>2026-02-03T05:18:11.002Z</v>
+      </c>
+      <c r="D256">
+        <v>28.542544921025833</v>
+      </c>
+      <c r="E256">
+        <v>77.33424189428794</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>user_4cjxcqgzc</v>
+      </c>
+      <c r="B257" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C257" t="str">
+        <v>2026-02-04T11:50:12.224Z</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>user_p347q3b5e</v>
+      </c>
+      <c r="B258" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C258" t="str">
+        <v>2026-02-04T14:08:28.623Z</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>user_f7x52mtra</v>
+      </c>
+      <c r="B259" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C259" t="str">
+        <v>2026-02-05T02:30:11.707Z</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>user_1kd0c2cf6</v>
+      </c>
+      <c r="B260" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C260" t="str">
+        <v>2026-02-05T09:53:18.828Z</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>user_xlyzqr0r8</v>
+      </c>
+      <c r="B261" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C261" t="str">
+        <v>2026-02-05T10:18:44.698Z</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>user_vgdohsmnc</v>
+      </c>
+      <c r="B262" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C262" t="str">
+        <v>2026-02-05T13:19:47.035Z</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>user_hsoii9kbc</v>
+      </c>
+      <c r="B263" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C263" t="str">
+        <v>2026-02-06T10:31:30.861Z</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>user_an65ny2ua</v>
+      </c>
+      <c r="B264" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C264" t="str">
+        <v>2026-02-07T18:56:38.178Z</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>user_cli7m5x7j</v>
+      </c>
+      <c r="B265" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C265" t="str">
+        <v>2026-02-09T13:42:47.705Z</v>
+      </c>
+      <c r="D265">
+        <v>12.960970015953423</v>
+      </c>
+      <c r="E265">
+        <v>77.64581450993407</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>user_977ht1isk</v>
+      </c>
+      <c r="B266" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C266" t="str">
+        <v>2026-02-09T14:03:10.976Z</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>user_mo3ln7e8s</v>
+      </c>
+      <c r="B267" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C267" t="str">
+        <v>2026-02-09T21:36:21.959Z</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>user_g2vw2q8wl</v>
+      </c>
+      <c r="B268" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C268" t="str">
+        <v>2026-02-10T16:33:50.510Z</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>user_v54f7oxh7</v>
+      </c>
+      <c r="B269" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C269" t="str">
+        <v>2026-02-11T05:53:10.938Z</v>
+      </c>
+      <c r="D269">
+        <v>18.45147714734051</v>
+      </c>
+      <c r="E269">
+        <v>73.81499553145169</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>user_fit1nfnz0</v>
+      </c>
+      <c r="B270" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C270" t="str">
+        <v>2026-02-15T14:27:49.030Z</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>user_n9ma3gzak</v>
+      </c>
+      <c r="B271" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C271" t="str">
+        <v>2026-02-16T19:40:50.034Z</v>
+      </c>
+      <c r="D271">
+        <v>37.69536521338391</v>
+      </c>
+      <c r="E271">
+        <v>-121.88991850727027</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>user_6x8t9setn</v>
+      </c>
+      <c r="B272" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C272" t="str">
+        <v>2026-02-16T22:50:10.551Z</v>
+      </c>
+      <c r="D272">
+        <v>53.41121924973484</v>
+      </c>
+      <c r="E272">
+        <v>-2.328908494765342</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>user_up3hep9jf</v>
+      </c>
+      <c r="B273" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C273" t="str">
+        <v>2026-02-17T04:17:58.201Z</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>user_2tpzbxa5g</v>
+      </c>
+      <c r="B274" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C274" t="str">
+        <v>2026-02-18T07:13:52.604Z</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>user_owlmpg2y8</v>
+      </c>
+      <c r="B275" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C275" t="str">
+        <v>2026-02-20T05:37:40.123Z</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>user_981nuv5i8</v>
+      </c>
+      <c r="B276" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C276" t="str">
+        <v>2026-02-20T05:41:11.042Z</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>user_u2w9ug2wu</v>
+      </c>
+      <c r="B277" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C277" t="str">
+        <v>2026-02-20T17:23:09.429Z</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>user_nu1q3c0c5</v>
+      </c>
+      <c r="B278" t="str">
+        <v>103.211.18.98</v>
+      </c>
+      <c r="C278" t="str">
+        <v>2026-02-21T06:32:43.360Z</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>user_lbxoce2cn</v>
+      </c>
+      <c r="B279" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C279" t="str">
+        <v>2026-02-22T19:21:20.378Z</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>user_u70znpmvq</v>
+      </c>
+      <c r="B280" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C280" t="str">
+        <v>2026-02-23T06:52:15.498Z</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>user_8lqhtzcl1</v>
+      </c>
+      <c r="B281" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C281" t="str">
+        <v>2026-02-23T14:36:10.828Z</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>user_4p4w0kdsk</v>
+      </c>
+      <c r="B282" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C282" t="str">
+        <v>2026-02-24T05:40:00.465Z</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>user_lyvlqzaqo</v>
+      </c>
+      <c r="B283" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C283" t="str">
+        <v>2026-02-24T09:06:14.984Z</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>user_ndjg9e8gs</v>
+      </c>
+      <c r="B284" t="str">
+        <v>121.240.135.194</v>
+      </c>
+      <c r="C284" t="str">
+        <v>2026-02-24T12:05:15.973Z</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>user_kyfnimbek</v>
+      </c>
+      <c r="B285" t="str">
+        <v>58.182.48.13</v>
+      </c>
+      <c r="C285" t="str">
+        <v>2026-02-25T04:35:29.579Z</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>user_nllwor7ry</v>
+      </c>
+      <c r="B286" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C286" t="str">
+        <v>2026-02-25T04:38:42.562Z</v>
+      </c>
+      <c r="D286">
+        <v>19.6058176</v>
+      </c>
+      <c r="E286">
+        <v>80.3618565</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>user_h7bv3va28</v>
+      </c>
+      <c r="B287" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C287" t="str">
+        <v>2026-02-25T10:17:35.203Z</v>
+      </c>
+      <c r="D287">
+        <v>25.1781554</v>
+      </c>
+      <c r="E287">
+        <v>56.3514645</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>user_76nc3i2un</v>
+      </c>
+      <c r="B288" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C288" t="str">
+        <v>2026-02-25T11:03:48.756Z</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>user_xw3j8p2ix</v>
+      </c>
+      <c r="B289" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C289" t="str">
+        <v>2026-02-25T18:42:51.651Z</v>
+      </c>
+      <c r="D289">
+        <v>16.47611</v>
+      </c>
+      <c r="E289">
+        <v>80.7054252</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>user_fsfrjbdvc</v>
+      </c>
+      <c r="B290" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C290" t="str">
+        <v>2026-02-26T09:35:41.464Z</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>user_82w6u2q5z</v>
+      </c>
+      <c r="B291" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C291" t="str">
+        <v>2026-02-26T17:35:46.515Z</v>
+      </c>
+      <c r="D291">
+        <v>18.5620663</v>
+      </c>
+      <c r="E291">
+        <v>73.8931459</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>user_urdb41dtr</v>
+      </c>
+      <c r="B292" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C292" t="str">
+        <v>2026-03-01T15:15:18.445Z</v>
+      </c>
+      <c r="D292">
+        <v>28.61</v>
+      </c>
+      <c r="E292">
+        <v>77.23</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>user_nj955zx5i</v>
+      </c>
+      <c r="B293" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C293" t="str">
+        <v>2026-03-02T05:00:09.374Z</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>user_xa5clfz05</v>
+      </c>
+      <c r="B294" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C294" t="str">
+        <v>2026-03-02T05:53:57.688Z</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>user_n0cisspc2</v>
+      </c>
+      <c r="B295" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C295" t="str">
+        <v>2026-03-03T07:21:51.011Z</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>user_vwsj5nn7q</v>
+      </c>
+      <c r="B296" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C296" t="str">
+        <v>2026-03-03T10:21:51.370Z</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>user_upjjnlb3r</v>
+      </c>
+      <c r="B297" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C297" t="str">
+        <v>2026-03-03T16:14:21.307Z</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>user_8k80iwadv</v>
+      </c>
+      <c r="B298" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C298" t="str">
+        <v>2026-03-04T05:50:22.990Z</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>user_ew9nj80xh</v>
+      </c>
+      <c r="B299" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C299" t="str">
+        <v>2026-03-04T08:24:59.735Z</v>
+      </c>
+      <c r="D299">
+        <v>51.8992299</v>
+      </c>
+      <c r="E299">
+        <v>-0.5101427</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>user_v7wy91wgi</v>
+      </c>
+      <c r="B300" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C300" t="str">
+        <v>2026-03-06T07:18:46.791Z</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>user_e0d0ifo9d</v>
+      </c>
+      <c r="B301" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C301" t="str">
+        <v>2026-03-07T11:23:11.064Z</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>user_dvrtatk3y</v>
+      </c>
+      <c r="B302" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C302" t="str">
+        <v>2026-03-08T14:38:58.865Z</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>user_vl4cn0nxz</v>
+      </c>
+      <c r="B303" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C303" t="str">
+        <v>2026-03-09T06:27:44.048Z</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>user_sk0fy02ba</v>
+      </c>
+      <c r="B304" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C304" t="str">
+        <v>2026-03-09T09:52:48.898Z</v>
+      </c>
+      <c r="D304">
+        <v>23.307474283093466</v>
+      </c>
+      <c r="E304">
+        <v>85.28931441627368</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>user_vgb5zh83y</v>
+      </c>
+      <c r="B305" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C305" t="str">
+        <v>2026-03-10T06:14:51.732Z</v>
+      </c>
+      <c r="D305">
+        <v>18.4875492</v>
+      </c>
+      <c r="E305">
+        <v>73.7964493</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>user_hlwbs8uzg</v>
+      </c>
+      <c r="B306" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C306" t="str">
+        <v>2026-03-10T11:23:02.712Z</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>user_z9ow2xonw</v>
+      </c>
+      <c r="B307" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C307" t="str">
+        <v>2026-03-10T14:06:56.697Z</v>
+      </c>
+      <c r="D307">
+        <v>37.695278</v>
+      </c>
+      <c r="E307">
+        <v>-121.8897305</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>user_3ddt3a9uc</v>
+      </c>
+      <c r="B308" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C308" t="str">
+        <v>2026-03-10T16:39:14.532Z</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>user_dpx0kpdcz</v>
+      </c>
+      <c r="B309" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C309" t="str">
+        <v>2026-03-10T18:14:29.754Z</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>user_iz96rs3nb</v>
+      </c>
+      <c r="B310" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C310" t="str">
+        <v>2026-03-11T05:36:04.409Z</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>user_dolc78bau</v>
+      </c>
+      <c r="B311" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C311" t="str">
+        <v>2026-03-12T17:35:42.778Z</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>user_4g2npeck7</v>
+      </c>
+      <c r="B312" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C312" t="str">
+        <v>2026-03-13T09:17:57.465Z</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>user_ctcv2a4ar</v>
+      </c>
+      <c r="B313" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C313" t="str">
+        <v>2026-03-13T09:26:21.044Z</v>
+      </c>
+      <c r="D313">
+        <v>18.4873437</v>
+      </c>
+      <c r="E313">
+        <v>73.8190054</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>user_6ki30u8xl</v>
+      </c>
+      <c r="B314" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C314" t="str">
+        <v>2026-03-13T10:12:57.233Z</v>
+      </c>
+      <c r="D314">
+        <v>18.5030528</v>
+      </c>
+      <c r="E314">
+        <v>73.9248952</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>user_j97h9wes4</v>
+      </c>
+      <c r="B315" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C315" t="str">
+        <v>2026-03-13T10:18:38.777Z</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>user_wgm7wf6j5</v>
+      </c>
+      <c r="B316" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C316" t="str">
+        <v>2026-03-13T13:35:01.861Z</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>user_cg6w2jws1</v>
+      </c>
+      <c r="B317" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C317" t="str">
+        <v>2026-03-15T12:37:54.401Z</v>
+      </c>
+      <c r="D317">
+        <v>18.4896541</v>
+      </c>
+      <c r="E317">
+        <v>73.8123395</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>user_mxl103k74</v>
+      </c>
+      <c r="B318" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C318" t="str">
+        <v>2026-03-15T23:55:50.793Z</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
+        <v>user_eiasp4qou</v>
+      </c>
+      <c r="B319" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C319" t="str">
+        <v>2026-03-16T14:11:01.216Z</v>
+      </c>
+      <c r="D319">
+        <v>18.486295</v>
+      </c>
+      <c r="E319">
+        <v>73.858585</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>user_4y12oai47</v>
+      </c>
+      <c r="B320" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C320" t="str">
+        <v>2026-03-17T19:47:19.670Z</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>user_5jz2r7f3t</v>
+      </c>
+      <c r="B321" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C321" t="str">
+        <v>2026-03-17T21:06:42.685Z</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>user_z56b2rhz9</v>
+      </c>
+      <c r="B322" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C322" t="str">
+        <v>2026-03-18T09:08:49.008Z</v>
+      </c>
+      <c r="D322">
+        <v>18.4531777</v>
+      </c>
+      <c r="E322">
+        <v>74.5693031</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>user_irp8ir6j9</v>
+      </c>
+      <c r="B323" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C323" t="str">
+        <v>2026-03-18T11:23:20.367Z</v>
+      </c>
+      <c r="D323">
+        <v>18.92600565492235</v>
+      </c>
+      <c r="E323">
+        <v>72.83341328051</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>user_75krv6dfb</v>
+      </c>
+      <c r="B324" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C324" t="str">
+        <v>2026-03-18T12:45:31.738Z</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>user_6gaplnls0</v>
+      </c>
+      <c r="B325" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C325" t="str">
+        <v>2026-03-18T13:09:18.615Z</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>user_q0syvs0fa</v>
+      </c>
+      <c r="B326" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C326" t="str">
+        <v>2026-03-18T13:34:02.982Z</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>user_2kwcnycl4</v>
+      </c>
+      <c r="B327" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C327" t="str">
+        <v>2026-03-18T16:31:14.555Z</v>
+      </c>
+      <c r="D327">
+        <v>23.03729035096823</v>
+      </c>
+      <c r="E327">
+        <v>72.55770116676372</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>user_2h0hubnxh</v>
+      </c>
+      <c r="B328" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C328" t="str">
+        <v>2026-03-19T02:47:24.555Z</v>
+      </c>
+      <c r="D328">
+        <v>22.587565778786104</v>
+      </c>
+      <c r="E328">
+        <v>88.35103175546145</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>user_o4jjfmqsd</v>
+      </c>
+      <c r="B329" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C329" t="str">
+        <v>2026-03-19T02:48:49.993Z</v>
+      </c>
+      <c r="D329">
+        <v>22.587795890627792</v>
+      </c>
+      <c r="E329">
+        <v>88.35106434056436</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>user_yh04l838l</v>
+      </c>
+      <c r="B330" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C330" t="str">
+        <v>2026-03-19T06:33:46.855Z</v>
+      </c>
+      <c r="D330">
+        <v>31.2514015</v>
+      </c>
+      <c r="E330">
+        <v>75.7025295</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>user_z5w9thn9g</v>
+      </c>
+      <c r="B331" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C331" t="str">
+        <v>2026-03-19T07:04:03.194Z</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>user_fbj7t6edc</v>
+      </c>
+      <c r="B332" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C332" t="str">
+        <v>2026-03-19T08:39:19.192Z</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>user_d0jvkpn08</v>
+      </c>
+      <c r="B333" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C333" t="str">
+        <v>2026-03-19T12:24:49.341Z</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>user_u9rvyqj48</v>
+      </c>
+      <c r="B334" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C334" t="str">
+        <v>2026-03-20T04:25:45.818Z</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>user_1w93ny2ae</v>
+      </c>
+      <c r="B335" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C335" t="str">
+        <v>2026-03-20T06:52:38.116Z</v>
+      </c>
+      <c r="D335">
+        <v>13.007475097663086</v>
+      </c>
+      <c r="E335">
+        <v>77.68334543790166</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>user_xgp5s4uuk</v>
+      </c>
+      <c r="B336" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C336" t="str">
+        <v>2026-03-20T07:08:26.798Z</v>
+      </c>
+      <c r="D336">
+        <v>18.5907389</v>
+      </c>
+      <c r="E336">
+        <v>73.7424262</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>user_hjc0kdrkn</v>
+      </c>
+      <c r="B337" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C337" t="str">
+        <v>2026-03-20T12:39:28.363Z</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>user_esx00fulp</v>
+      </c>
+      <c r="B338" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C338" t="str">
+        <v>2026-03-20T12:40:51.219Z</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>user_a6cn0r5te</v>
+      </c>
+      <c r="B339" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C339" t="str">
+        <v>2026-03-20T12:41:53.592Z</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>user_9a4iwm1pw</v>
+      </c>
+      <c r="B340" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C340" t="str">
+        <v>2026-03-21T14:59:32.788Z</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>user_r51aisnt1</v>
+      </c>
+      <c r="B341" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C341" t="str">
+        <v>2026-03-23T17:30:32.020Z</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>user_hsbv3kqgc</v>
+      </c>
+      <c r="B342" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C342" t="str">
+        <v>2026-03-24T01:53:38.455Z</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>user_ng1k86wbd</v>
+      </c>
+      <c r="B343" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C343" t="str">
+        <v>2026-03-24T10:22:09.579Z</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>user_hk8vc5cvv</v>
+      </c>
+      <c r="B344" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C344" t="str">
+        <v>2026-03-27T22:16:27.442Z</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>user_y4in23ajz</v>
+      </c>
+      <c r="B345" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C345" t="str">
+        <v>2026-03-28T11:13:00.866Z</v>
+      </c>
+      <c r="D345">
+        <v>18.3978688</v>
+      </c>
+      <c r="E345">
+        <v>73.9144352</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>user_65ynl9m8c</v>
+      </c>
+      <c r="B346" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C346" t="str">
+        <v>2026-03-29T14:04:17.161Z</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>user_lvsuj7zez</v>
+      </c>
+      <c r="B347" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C347" t="str">
+        <v>2026-03-30T05:56:29.100Z</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>user_kjfgotipu</v>
+      </c>
+      <c r="B348" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C348" t="str">
+        <v>2026-03-30T09:05:19.451Z</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>user_vbo2jdv5w</v>
+      </c>
+      <c r="B349" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C349" t="str">
+        <v>2026-03-30T09:10:41.482Z</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>user_71k5xt0xw</v>
+      </c>
+      <c r="B350" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C350" t="str">
+        <v>2026-03-31T11:39:50.861Z</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>user_n2az78n03</v>
+      </c>
+      <c r="B351" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C351" t="str">
+        <v>2026-03-31T11:48:36.875Z</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>user_67fkpbffw</v>
+      </c>
+      <c r="B352" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C352" t="str">
+        <v>2026-04-02T06:24:25.381Z</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>user_s4eotabhy</v>
+      </c>
+      <c r="B353" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C353" t="str">
+        <v>2026-04-03T14:07:48.158Z</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>user_wd991cb9q</v>
+      </c>
+      <c r="B354" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C354" t="str">
+        <v>2026-04-03T14:42:34.320Z</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>user_v33h3upxx</v>
+      </c>
+      <c r="B355" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C355" t="str">
+        <v>2026-04-04T12:05:13.225Z</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>user_w0ni5mlzy</v>
+      </c>
+      <c r="B356" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C356" t="str">
+        <v>2026-04-05T16:14:17.930Z</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v>user_x9s2mf0kr</v>
+      </c>
+      <c r="B357" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C357" t="str">
+        <v>2026-04-06T12:59:05.733Z</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="str">
+        <v>user_c4v5ywwxc</v>
+      </c>
+      <c r="B358" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C358" t="str">
+        <v>2026-04-08T13:18:19.041Z</v>
+      </c>
+      <c r="D358">
+        <v>18.7000579</v>
+      </c>
+      <c r="E358">
+        <v>73.7106574</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="str">
+        <v>user_5dveq7h6e</v>
+      </c>
+      <c r="B359" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C359" t="str">
+        <v>2026-04-08T22:30:26.169Z</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="str">
+        <v>user_l6jr2bo8t</v>
+      </c>
+      <c r="B360" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C360" t="str">
+        <v>2026-04-09T11:33:19.038Z</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="str">
+        <v>user_qzqad8h4b</v>
+      </c>
+      <c r="B361" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C361" t="str">
+        <v>2026-04-09T12:06:55.613Z</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="str">
+        <v>user_5i1ugrtrh</v>
+      </c>
+      <c r="B362" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C362" t="str">
+        <v>2026-04-10T16:23:45.681Z</v>
+      </c>
+      <c r="D362">
+        <v>19.1706174</v>
+      </c>
+      <c r="E362">
+        <v>72.882136</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="str">
+        <v>user_e3ya91ejd</v>
+      </c>
+      <c r="B363" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C363" t="str">
+        <v>2026-04-11T07:09:22.110Z</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="str">
+        <v>user_701pttglq</v>
+      </c>
+      <c r="B364" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C364" t="str">
+        <v>2026-04-11T10:57:10.990Z</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v>user_a9zw0g8j4</v>
+      </c>
+      <c r="B365" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C365" t="str">
+        <v>2026-04-12T23:00:04.692Z</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="str">
+        <v>user_2ay7zyctv</v>
+      </c>
+      <c r="B366" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C366" t="str">
+        <v>2026-04-13T10:38:08.986Z</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v>user_1dr2gjs7m</v>
+      </c>
+      <c r="B367" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C367" t="str">
+        <v>2026-04-14T08:49:08.452Z</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="str">
+        <v>user_7ifnhyvdn</v>
+      </c>
+      <c r="B368" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C368" t="str">
+        <v>2026-04-16T04:19:19.991Z</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v>user_gfu516mup</v>
+      </c>
+      <c r="B369" t="str">
+        <v>103.41.75.133</v>
+      </c>
+      <c r="C369" t="str">
+        <v>2026-04-16T07:06:43.875Z</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="str">
+        <v>user_n11gr7qck</v>
+      </c>
+      <c r="B370" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C370" t="str">
+        <v>2026-04-16T08:18:47.940Z</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v>user_7fvm0jhe8</v>
+      </c>
+      <c r="B371" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C371" t="str">
+        <v>2026-04-16T08:50:50.589Z</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="str">
+        <v>user_6ffm9i2h6</v>
+      </c>
+      <c r="B372" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C372" t="str">
+        <v>2026-04-16T11:49:45.916Z</v>
+      </c>
+      <c r="D372">
+        <v>18.5010738</v>
+      </c>
+      <c r="E372">
+        <v>73.7909167</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v>user_zdqpkp8qc</v>
+      </c>
+      <c r="B373" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C373" t="str">
+        <v>2026-04-17T09:42:53.163Z</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="str">
+        <v>user_21o0sj7p4</v>
+      </c>
+      <c r="B374" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C374" t="str">
+        <v>2026-04-18T02:42:17.577Z</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v>user_gy60feup9</v>
+      </c>
+      <c r="B375" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C375" t="str">
+        <v>2026-04-20T06:43:54.203Z</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>user_jld44hdee</v>
+      </c>
+      <c r="B376" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C376" t="str">
+        <v>2026-04-20T07:35:58.671Z</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>user_18kdafyjd</v>
+      </c>
+      <c r="B377" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C377" t="str">
+        <v>2026-04-21T05:26:03.189Z</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>user_uoh5ovhnr</v>
+      </c>
+      <c r="B378" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C378" t="str">
+        <v>2026-04-21T09:31:10.122Z</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v>user_hcqdnnltl</v>
+      </c>
+      <c r="B379" t="str">
+        <v>::ffff:127.0.0.1</v>
+      </c>
+      <c r="C379" t="str">
+        <v>2026-04-22T07:17:55.785Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E379"/>
   </ignoredErrors>
 </worksheet>
 </file>